--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484244_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484244_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.592</v>
+        <v>3.709</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4638</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1281</v>
+        <v>2.7196</v>
       </c>
       <c r="G2" t="n">
         <v>3.4023</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0056</v>
+        <v>0.1113</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0894</v>
+        <v>-0.5639</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0838</v>
+        <v>0.6752</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3864</v>
+        <v>2.0015</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2089</v>
+        <v>0.2155</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5953</v>
+        <v>1.7859</v>
       </c>
       <c r="G3" t="n">
         <v>2.2417</v>
@@ -688,13 +688,13 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9101</v>
+        <v>-0.2951</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.652</v>
+        <v>-0.2276</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2582</v>
+        <v>-0.0675</v>
       </c>
       <c r="V3" t="n">
         <v>0.0549</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2158</v>
+        <v>1.2711</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4316</v>
+        <v>0.2808</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6475</v>
+        <v>0.9902</v>
       </c>
       <c r="G4" t="n">
-        <v>0.156</v>
+        <v>4.0526</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3694</v>
+        <v>0.437</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5255</v>
+        <v>3.6157</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1811</v>
+        <v>4.2123</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7496</v>
+        <v>0.596</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9307</v>
+        <v>3.6163</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0251</v>
+        <v>-0.1597</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3802</v>
+        <v>-0.1591</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4052</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3441</v>
+        <v>-3.9069</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0598</v>
+        <v>-0.0467</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4541</v>
+        <v>-0.0246</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6056</v>
+        <v>-0.0221</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1187</v>
+        <v>1.194</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5642</v>
+        <v>-2.3315</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5545</v>
+        <v>3.5254</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0526</v>
+        <v>1.8344</v>
       </c>
       <c r="H5" t="n">
-        <v>0.437</v>
+        <v>0.7813</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6157</v>
+        <v>1.0531</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2123</v>
+        <v>0.8455</v>
       </c>
       <c r="K5" t="n">
-        <v>0.596</v>
+        <v>0.3313</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6163</v>
+        <v>0.5142</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1597</v>
+        <v>0.9889</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1591</v>
+        <v>0.45</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.5389</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.7348</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9069</v>
+        <v>-3.3208</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1991</v>
+        <v>0.5317</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2588</v>
+        <v>0.1439</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4579</v>
+        <v>0.3878</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9875</v>
+        <v>0.7145</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7558</v>
+        <v>-1.7151</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7433</v>
+        <v>2.4296</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8344</v>
+        <v>0.156</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7813</v>
+        <v>-0.3694</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0531</v>
+        <v>0.5255</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8455</v>
+        <v>0.1811</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3313</v>
+        <v>-0.7496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5142</v>
+        <v>0.9307</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9889</v>
+        <v>-0.0251</v>
       </c>
       <c r="N6" t="n">
-        <v>0.45</v>
+        <v>0.3802</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5389</v>
+        <v>-0.4052</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.3208</v>
+        <v>-2.3441</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3252</v>
+        <v>0.5585</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2805</v>
+        <v>0.1707</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6056</v>
+        <v>0.3878</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3807</v>
+        <v>-0.2445</v>
       </c>
       <c r="E7" t="n">
         <v>0.7103</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.091</v>
+        <v>-0.9548</v>
       </c>
       <c r="G7" t="n">
         <v>1.1378</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2999</v>
+        <v>-0.1637</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1183</v>
+        <v>0.0178</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2186</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1491</v>
+        <v>-1.9092</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0983</v>
+        <v>-1.9625</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0508</v>
+        <v>0.0533</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.4929</v>
+        <v>-1.6261</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7961</v>
+        <v>-1.9358</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6968</v>
+        <v>0.3097</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.0037</v>
+        <v>-1.2668</v>
       </c>
       <c r="K8" t="n">
         <v>-1.3073</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.6964</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4893</v>
+        <v>-0.3593</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4889</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0004</v>
+        <v>0.2692</v>
       </c>
       <c r="P8" t="n">
         <v>0.3907</v>
@@ -1078,19 +1078,19 @@
         <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3438</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.296</v>
+        <v>-0.0315</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0478</v>
+        <v>0.0219</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1659</v>
+        <v>-2.6131</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1647</v>
+        <v>-1.4303</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0012</v>
+        <v>-1.1828</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6261</v>
+        <v>0.6959</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9358</v>
+        <v>0.1973</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3097</v>
+        <v>0.4986</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2668</v>
+        <v>1.4647</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3073</v>
+        <v>0.6958</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>0.7688</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3593</v>
+        <v>-0.7688</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.4986</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2692</v>
+        <v>-0.2702</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2663</v>
+        <v>-0.5276</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2337</v>
+        <v>-0.7462</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0326</v>
+        <v>0.2186</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6642</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6325</v>
+        <v>-2.6264</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5314</v>
+        <v>-0.8148</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1011</v>
+        <v>-1.8117</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6959</v>
+        <v>-1.1217</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1973</v>
+        <v>-0.6633</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4986</v>
+        <v>-0.4583</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4647</v>
+        <v>-0.5727</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6958</v>
+        <v>0.0205</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7688</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7688</v>
+        <v>-0.549</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4986</v>
+        <v>-0.6838</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2702</v>
+        <v>0.1348</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.547</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.0467</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3003</v>
+        <v>-0.044</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6809</v>
+        <v>-2.9853</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8148</v>
+        <v>-2.9072</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8661</v>
+        <v>-0.078</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1217</v>
+        <v>-4.4929</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6633</v>
+        <v>-1.7961</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4583</v>
+        <v>-2.6968</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5727</v>
+        <v>-4.0037</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0205</v>
+        <v>-1.3073</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-2.6964</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.549</v>
+        <v>-0.4893</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6838</v>
+        <v>-0.4889</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1348</v>
+        <v>-0.0004</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1453</v>
+        <v>0.5077</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0467</v>
+        <v>0.4871</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0985</v>
+        <v>0.0206</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8897</v>
+        <v>-4.5046</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8927</v>
+        <v>-2.5894</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.997</v>
+        <v>-1.9153</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3033</v>
@@ -1390,13 +1390,13 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7269</v>
+        <v>-0.3418</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4099</v>
+        <v>-0.1065</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.317</v>
+        <v>-0.2353</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6642</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.598399999999999</v>
+        <v>-5.993000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.1599</v>
+        <v>-11.5548</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5615</v>
+        <v>5.5614</v>
       </c>
       <c r="G13" t="n">
-        <v>2.976699999999999</v>
+        <v>2.9767</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0716</v>
+        <v>-1.071599999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>4.048599999999999</v>
+        <v>4.048600000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>4.548299999999999</v>
+        <v>4.548300000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4947999999999998</v>
+        <v>0.4948</v>
       </c>
       <c r="L13" t="n">
-        <v>4.0534</v>
+        <v>4.053399999999998</v>
       </c>
       <c r="M13" t="n">
         <v>-1.5716</v>
@@ -1456,7 +1456,7 @@
         <v>-1.5667</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.004999999999999893</v>
+        <v>-0.005000000000000004</v>
       </c>
       <c r="P13" t="n">
         <v>-4.883499999999999</v>
@@ -1468,16 +1468,16 @@
         <v>12.6973</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3714</v>
+        <v>0.2339</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7322</v>
+        <v>-1.1269</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3606</v>
+        <v>1.3608</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.319999999999999</v>
+        <v>-4.32</v>
       </c>
       <c r="W13" t="n">
         <v>2.6047</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.3573</v>
+        <v>8.2317</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7344</v>
+        <v>6.2288</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6229</v>
+        <v>2.0028</v>
       </c>
       <c r="G14" t="n">
         <v>2.9809</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.2097</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2726</v>
+        <v>-0.233</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3567</v>
+        <v>0.0233</v>
       </c>
       <c r="V14" t="n">
         <v>4.8745</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.701</v>
+        <v>2.5191</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6517</v>
+        <v>0.9328</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0493</v>
+        <v>1.5863</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0636</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5377</v>
+        <v>1.3557</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3416</v>
+        <v>0.6227</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1961</v>
+        <v>0.7331</v>
       </c>
       <c r="V15" t="n">
         <v>0.0549</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6706</v>
+        <v>2.1141</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4989</v>
+        <v>-0.2728</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1717</v>
+        <v>2.387</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2934</v>
+        <v>1.5267</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2131</v>
+        <v>2.2535</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0803</v>
+        <v>-0.7268</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1007</v>
+        <v>0.1233</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1817</v>
+        <v>2.3331</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>-2.2098</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3942</v>
+        <v>1.4035</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3948</v>
+        <v>-0.0795</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>1.483</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1855</v>
+        <v>-0.78</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4237</v>
+        <v>-0.2008</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2381</v>
+        <v>-0.5792</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4101</v>
+        <v>2.0219</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6773</v>
+        <v>-0.7043</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0874</v>
+        <v>2.7262</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5267</v>
+        <v>1.0707</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2535</v>
+        <v>0.8823</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7268</v>
+        <v>0.1883</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1233</v>
+        <v>0.5467</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3331</v>
+        <v>0.4924</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.2098</v>
+        <v>0.0543</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4035</v>
+        <v>0.5239</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0795</v>
+        <v>0.3899</v>
       </c>
       <c r="O17" t="n">
-        <v>1.483</v>
+        <v>0.134</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4841</v>
+        <v>-0.0255</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6052</v>
+        <v>-0.079</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8788</v>
+        <v>0.0535</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2111</v>
+        <v>1.9648</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0327</v>
+        <v>0.9034</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1784</v>
+        <v>1.0614</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4644</v>
+        <v>0.2934</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6961</v>
+        <v>0.2131</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7683</v>
+        <v>0.0803</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2939</v>
+        <v>-0.1007</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3111</v>
+        <v>-0.1817</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9828</v>
+        <v>0.0809</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8295</v>
+        <v>0.3942</v>
       </c>
       <c r="N18" t="n">
-        <v>0.385</v>
+        <v>0.3948</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2146</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7467</v>
+        <v>0.1086</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3331</v>
+        <v>-0.0192</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4136</v>
+        <v>0.1278</v>
       </c>
       <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X18" t="n">
         <v>-1.2186</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-0.6642</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.5545</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1135</v>
+        <v>1.7008</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9058</v>
+        <v>1.4114</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2077</v>
+        <v>0.2894</v>
       </c>
       <c r="G19" t="n">
         <v>1.3797</v>
@@ -1936,13 +1936,13 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2895</v>
+        <v>0.2978</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6052</v>
+        <v>-0.0997</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3158</v>
+        <v>0.3975</v>
       </c>
       <c r="V19" t="n">
         <v>0.6093</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8797</v>
+        <v>0.778</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4121</v>
+        <v>-0.3718</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2918</v>
+        <v>1.1498</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0707</v>
+        <v>2.4644</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8823</v>
+        <v>1.6961</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1883</v>
+        <v>0.7683</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5467</v>
+        <v>3.2939</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4924</v>
+        <v>1.3111</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0543</v>
+        <v>1.9828</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5239</v>
+        <v>-0.8295</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3899</v>
+        <v>0.385</v>
       </c>
       <c r="O20" t="n">
-        <v>0.134</v>
+        <v>-1.2146</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
         <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1677</v>
+        <v>0.3137</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3809</v>
+        <v>0.385</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3169</v>
+        <v>-1.246</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1895</v>
+        <v>-2.8199</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8726</v>
+        <v>1.574</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8683</v>
+        <v>-2.1388</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.099</v>
+        <v>-2.3137</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7692</v>
+        <v>0.1749</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.979</v>
+        <v>-1.3192</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0195</v>
+        <v>-2.5736</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>1.2544</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8893</v>
+        <v>-0.8196</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0795</v>
+        <v>0.2599</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8097</v>
+        <v>-1.0795</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5514</v>
+        <v>0.1114</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0384</v>
+        <v>-0.3287</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5898</v>
+        <v>0.4401</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5285</v>
+        <v>-1.6825</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0222</v>
+        <v>-2.3917</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4936</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1388</v>
+        <v>-1.8683</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3137</v>
+        <v>-1.099</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1749</v>
+        <v>-0.7692</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3192</v>
+        <v>-0.979</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.5736</v>
+        <v>-1.0195</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2544</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8196</v>
+        <v>-0.8893</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2599</v>
+        <v>-0.0795</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>-0.8097</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1711</v>
+        <v>0.1857</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5309</v>
+        <v>-0.2406</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3598</v>
+        <v>0.4264</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0744</v>
+        <v>-3.7983</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2486</v>
+        <v>-3.9453</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1742</v>
+        <v>0.147</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0486</v>
@@ -2248,13 +2248,13 @@
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1392</v>
+        <v>0.1369</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.652</v>
+        <v>-0.3486</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5128</v>
+        <v>0.4855</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2772</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8251</v>
+        <v>-5.3311</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8354</v>
+        <v>-4.532</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9897</v>
+        <v>-0.7991</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5732</v>
@@ -2326,13 +2326,13 @@
         <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9431</v>
+        <v>-0.4491</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2774</v>
+        <v>-0.0867</v>
       </c>
       <c r="V24" t="n">
         <v>0.2772</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.598399999999997</v>
+        <v>7.272500000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5616</v>
+        <v>-5.561400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>12.1599</v>
+        <v>12.834</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9767</v>
+        <v>-2.976700000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0718</v>
+        <v>1.071799999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-4.0485</v>
@@ -2380,10 +2380,10 @@
         <v>1.571699999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>1.566599999999999</v>
+        <v>1.566600000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004899999999999682</v>
+        <v>0.004899999999999238</v>
       </c>
       <c r="M25" t="n">
         <v>-4.5482</v>
@@ -2404,13 +2404,13 @@
         <v>17.5809</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3715000000000002</v>
+        <v>1.0455</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3606</v>
+        <v>-1.3607</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7322</v>
+        <v>2.4063</v>
       </c>
       <c r="V25" t="n">
         <v>4.3201</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484244_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484244_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.9247</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1494,7 +1555,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1562,6 +1623,11 @@
       </c>
       <c r="X14" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1572,7 +1638,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1640,6 +1706,11 @@
       </c>
       <c r="X15" t="n">
         <v>0.0549</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1650,7 +1721,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1718,6 +1789,11 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1728,7 +1804,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1796,6 +1872,11 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1806,7 +1887,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1874,45 +1955,50 @@
       </c>
       <c r="X18" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7008</v>
+        <v>1.3938</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4114</v>
+        <v>1.1044</v>
       </c>
       <c r="F19" t="n">
         <v>0.2894</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3797</v>
+        <v>1.0727</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1489</v>
+        <v>1.8419</v>
       </c>
       <c r="I19" t="n">
         <v>-0.7692</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6598</v>
+        <v>1.3528</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2934</v>
+        <v>1.9864</v>
       </c>
       <c r="L19" t="n">
         <v>-0.6336000000000001</v>
@@ -1952,231 +2038,246 @@
       </c>
       <c r="X19" t="n">
         <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.778</v>
+        <v>1.221</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3718</v>
+        <v>1.221</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1498</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4644</v>
+        <v>1.221</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6961</v>
+        <v>0.614</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7683</v>
+        <v>0.607</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2939</v>
+        <v>1.221</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3111</v>
+        <v>0.614</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9828</v>
+        <v>0.607</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2146</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3137</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.246</v>
+        <v>0.778</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8199</v>
+        <v>-0.3718</v>
       </c>
       <c r="F21" t="n">
-        <v>1.574</v>
+        <v>1.1498</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1388</v>
+        <v>2.4644</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3137</v>
+        <v>1.6961</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1749</v>
+        <v>0.7683</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3192</v>
+        <v>3.2939</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.5736</v>
+        <v>1.3111</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2544</v>
+        <v>1.9828</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8196</v>
+        <v>-0.8295</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2599</v>
+        <v>0.385</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0795</v>
+        <v>-1.2146</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1114</v>
+        <v>0.3137</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3287</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4401</v>
+        <v>0.385</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6825</v>
+        <v>0.307</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3917</v>
+        <v>0.307</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7092000000000001</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8683</v>
+        <v>0.307</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.099</v>
+        <v>0.307</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7692</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.979</v>
+        <v>0.307</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0195</v>
+        <v>0.307</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8893</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0795</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8097</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1857</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2406</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4264</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2186,241 +2287,423 @@
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7983</v>
+        <v>-1.246</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9453</v>
+        <v>-2.8199</v>
       </c>
       <c r="F23" t="n">
-        <v>0.147</v>
+        <v>1.574</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.0486</v>
+        <v>-2.1388</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3088</v>
+        <v>-2.3137</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7398</v>
+        <v>0.1749</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6199</v>
+        <v>-1.3192</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9596</v>
+        <v>-2.5736</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6603</v>
+        <v>1.2544</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4287</v>
+        <v>-0.8196</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3492</v>
+        <v>0.2599</v>
       </c>
       <c r="O23" t="n">
         <v>-1.0795</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1369</v>
+        <v>0.1114</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3486</v>
+        <v>-0.3287</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4855</v>
+        <v>0.4401</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3311</v>
+        <v>-1.6825</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.532</v>
+        <v>-2.3917</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7991</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.5732</v>
+        <v>-1.8683</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6989</v>
+        <v>-1.099</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8743</v>
+        <v>-0.7692</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2748</v>
+        <v>-0.979</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9404</v>
+        <v>-1.0195</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3344</v>
+        <v>0.0405</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2984</v>
+        <v>-0.8893</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7585</v>
+        <v>-0.0795</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5399</v>
+        <v>-0.8097</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4491</v>
+        <v>0.1857</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3624</v>
+        <v>-0.2406</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0867</v>
+        <v>0.4264</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.272500000000002</v>
+        <v>-5.0192</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.561400000000001</v>
+        <v>-5.1662</v>
       </c>
       <c r="F25" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-5.2696</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.9228</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.3468</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.8409</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.5736</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.2673</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.4287</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.0795</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.3486</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.4855</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>G. LOZANO MASSANET</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.3311</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.532</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.7991</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.5732</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.6989</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.8743</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-3.2748</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.9404</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.3344</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.2984</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7585</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.4491</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.3624</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.0867</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484244_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7.272599999999998</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-5.561300000000001</v>
+      </c>
+      <c r="F27" t="n">
         <v>12.834</v>
       </c>
-      <c r="G25" t="n">
-        <v>-2.976700000000001</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G27" t="n">
+        <v>-2.9767</v>
+      </c>
+      <c r="H27" t="n">
         <v>1.071799999999999</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>-4.0485</v>
       </c>
-      <c r="J25" t="n">
-        <v>1.571699999999999</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.566600000000001</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.004899999999999238</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="J27" t="n">
+        <v>1.571700000000001</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.566600000000002</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.004899999999999682</v>
+      </c>
+      <c r="M27" t="n">
         <v>-4.5482</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>-0.4948</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>-4.0535</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>4.883599999999999</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>-12.6973</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>17.5809</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>1.0455</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>-1.3607</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>2.4063</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>4.3201</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>6.9247</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-2.6047</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
